--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T06:28:21+00:00</t>
+    <t>2026-06-18T08:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2379" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2379" uniqueCount="511">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:24:24+00:00</t>
+    <t>2026-06-18T13:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This FHIR profile is defining the current smoking status observation for PreNUDGE. It is derived from the APS Observation Tobacco Use profile, which imposes the IPS Observation Social History - Tobacco Use profile. The value is derived from the ATHIS-based SmokingStatusQuestionnaire, primarily from SK1 and, if SK1 is negative, from the past tobacco smoking question.</t>
+    <t>This FHIR profile is defining the current smoking status observation for PreNUDGE. It is derived from the APS Observation Tobacco Use profile, which imposes the IPS Observation Social History - Tobacco Use profile. The value is derived from the ATHIS-based SmokingStatusQuestionnaire, primarily from SK1 and, if SK1 is negative, from the past tobacco smoking question. Additional fields from the PreNUDGE Observation profile are added.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1071,7 +1071,7 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>Actual result</t>
+    <t>Set to CodeableConcept, as recommended in Observation Social History - Tobacco Use (IPS)</t>
   </si>
   <si>
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
@@ -1105,6 +1105,9 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
+    <t>Actual result</t>
+  </si>
+  <si>
     <t>https://termgit.elga.gv.at/ValueSet/elga-currentsmokingstatus</t>
   </si>
   <si>
@@ -1289,7 +1292,7 @@
 </t>
   </si>
   <si>
-    <t>(Measurement) Device</t>
+    <t>(Measurement) Devices should be documented when used</t>
   </si>
   <si>
     <t>The device used to generate the observation data.</t>
@@ -1526,7 +1529,7 @@
     <t>Observation.component</t>
   </si>
   <si>
-    <t>Component results</t>
+    <t>Components should only be used when multiple values are inseparably connected to a single measurement (e.g., score domains).</t>
   </si>
   <si>
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
@@ -5875,7 +5878,7 @@
         <v>182</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="M33" t="s" s="2">
         <v>340</v>
@@ -5913,7 +5916,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>21</v>
@@ -5966,10 +5969,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5995,16 +5998,16 @@
         <v>182</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -6032,10 +6035,10 @@
         <v>187</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -6053,7 +6056,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6062,7 +6065,7 @@
         <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>105</v>
@@ -6077,7 +6080,7 @@
         <v>136</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
@@ -6088,14 +6091,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6117,16 +6120,16 @@
         <v>182</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -6154,10 +6157,10 @@
         <v>187</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -6175,7 +6178,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6193,27 +6196,27 @@
         <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6236,19 +6239,19 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -6297,7 +6300,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6318,10 +6321,10 @@
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
@@ -6332,10 +6335,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6361,13 +6364,13 @@
         <v>182</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6396,10 +6399,10 @@
         <v>269</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
@@ -6417,7 +6420,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6435,27 +6438,27 @@
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6481,16 +6484,16 @@
         <v>182</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6519,7 +6522,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -6537,7 +6540,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6558,10 +6561,10 @@
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>21</v>
@@ -6572,10 +6575,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6598,16 +6601,16 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6657,7 +6660,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6675,27 +6678,27 @@
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6709,7 +6712,7 @@
         <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -6718,16 +6721,16 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6777,7 +6780,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6795,27 +6798,27 @@
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6838,19 +6841,19 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6899,7 +6902,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6911,7 +6914,7 @@
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
@@ -6920,10 +6923,10 @@
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
@@ -6934,10 +6937,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7052,10 +7055,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7172,14 +7175,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7201,10 +7204,10 @@
         <v>139</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>142</v>
@@ -7259,7 +7262,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7294,10 +7297,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7320,13 +7323,13 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7377,7 +7380,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7386,7 +7389,7 @@
         <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>105</v>
@@ -7398,10 +7401,10 @@
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
@@ -7412,10 +7415,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7438,13 +7441,13 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7495,7 +7498,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7504,7 +7507,7 @@
         <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>105</v>
@@ -7516,10 +7519,10 @@
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>21</v>
@@ -7530,10 +7533,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7559,16 +7562,16 @@
         <v>182</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7596,10 +7599,10 @@
         <v>117</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7617,7 +7620,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7635,13 +7638,13 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>21</v>
@@ -7652,10 +7655,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7681,16 +7684,16 @@
         <v>182</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7718,10 +7721,10 @@
         <v>269</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -7739,7 +7742,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7757,13 +7760,13 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
@@ -7774,10 +7777,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7800,17 +7803,17 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -7859,7 +7862,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7883,7 +7886,7 @@
         <v>21</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>21</v>
@@ -7894,10 +7897,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7923,10 +7926,10 @@
         <v>160</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7977,7 +7980,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7998,10 +8001,10 @@
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>21</v>
@@ -8012,10 +8015,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8038,16 +8041,16 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8097,7 +8100,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8118,10 +8121,10 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
@@ -8132,10 +8135,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8158,16 +8161,16 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8217,7 +8220,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8238,10 +8241,10 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>21</v>
@@ -8252,10 +8255,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8278,19 +8281,19 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8339,7 +8342,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8360,10 +8363,10 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
@@ -8374,10 +8377,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8492,10 +8495,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8612,14 +8615,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8641,10 +8644,10 @@
         <v>139</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>142</v>
@@ -8699,7 +8702,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8734,10 +8737,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8763,13 +8766,13 @@
         <v>182</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>268</v>
@@ -8821,7 +8824,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>93</v>
@@ -8839,7 +8842,7 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>274</v>
@@ -8856,10 +8859,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8882,16 +8885,16 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M58" t="s" s="2">
         <v>340</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>342</v>
@@ -8943,7 +8946,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8961,7 +8964,7 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>345</v>
@@ -8978,10 +8981,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9007,16 +9010,16 @@
         <v>182</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -9044,10 +9047,10 @@
         <v>187</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>21</v>
@@ -9065,7 +9068,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9074,7 +9077,7 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
@@ -9089,7 +9092,7 @@
         <v>136</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>21</v>
@@ -9100,14 +9103,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9129,16 +9132,16 @@
         <v>182</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -9166,10 +9169,10 @@
         <v>187</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9187,7 +9190,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9205,27 +9208,27 @@
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9251,16 +9254,16 @@
         <v>83</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -9309,7 +9312,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9330,10 +9333,10 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>21</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:26:12+00:00</t>
+    <t>2026-06-22T11:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T11:44:44+00:00</t>
+    <t>2026-06-22T12:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:35:22+00:00</t>
+    <t>2026-06-22T13:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>93</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:57:07+00:00</t>
+    <t>2026-06-22T14:44:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:44:05+00:00</t>
+    <t>2026-06-24T07:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:32:55+00:00</t>
+    <t>2026-06-24T12:07:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:07:10+00:00</t>
+    <t>2026-06-24T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:18:54+00:00</t>
+    <t>2026-06-29T10:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:23:22+00:00</t>
+    <t>2026-06-29T10:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:47:49+00:00</t>
+    <t>2026-06-29T16:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T16:58:51+00:00</t>
+    <t>2026-06-29T17:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:35:07+00:00</t>
+    <t>2026-06-30T08:18:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:18:50+00:00</t>
+    <t>2026-06-30T14:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:49:39+00:00</t>
+    <t>2026-07-01T08:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:47:20+00:00</t>
+    <t>2026-07-01T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:20:10+00:00</t>
+    <t>2026-07-22T09:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:36+00:00</t>
+    <t>2026-07-22T10:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:33:49+00:00</t>
+    <t>2026-07-22T11:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T11:37:23+00:00</t>
+    <t>2026-07-23T14:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:49:55+00:00</t>
+    <t>2026-08-05T12:17:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:17:57+00:00</t>
+    <t>2026-08-05T12:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:30:06+00:00</t>
+    <t>2026-08-06T10:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:54:53+00:00</t>
+    <t>2026-08-07T08:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:52:23+00:00</t>
+    <t>2026-08-13T06:23:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}at-prenudge-result-present:A PreNUDGE Observation must contain a root result, a root data absent reason, or at least one component result or component data absent reason. {value.exists() or dataAbsentReason.exists() or component.where(value.exists() or dataAbsentReason.exists()).exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1114,7 +1114,7 @@
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
-    <t>Why the result is missing</t>
+    <t>Reason why no clinically or analytically meaningful result is available</t>
   </si>
   <si>
     <t>Provides a reason why the expected value in the element Observation.value[x] is missing.</t>
@@ -5967,7 +5967,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>352</v>
       </c>
@@ -5986,7 +5986,7 @@
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T06:23:48+00:00</t>
+    <t>2026-08-18T12:08:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:08:37+00:00</t>
+    <t>2026-08-18T12:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:35:51+00:00</t>
+    <t>2026-08-20T08:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:19:53+00:00</t>
+    <t>2026-08-20T13:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:42:02+00:00</t>
+    <t>2026-08-26T07:06:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:06:07+00:00</t>
+    <t>2026-08-26T07:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:22:28+00:00</t>
+    <t>2026-08-26T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
